--- a/power-apps-challenge/power-apps-challenge.xlsx
+++ b/power-apps-challenge/power-apps-challenge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\linkedin-learning\power-platform-for-excel-placeholder\files\3-build-custom-apps-with-power-apps\power-apps-challenge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\first-steps-with-power-apps-for-excel-users\power-apps-challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3AE700D-647D-4501-B910-E6CA02E608F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25047E42-9F93-4A53-BF61-E2254A4E6A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -265,7 +265,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}" name="Table1" displayName="Table1" ref="A1:E5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}" name="claims" displayName="claims" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{55F8BFD6-C4FC-4C00-B089-DA9A0648BD4A}" name="Property ID"/>
@@ -542,15 +542,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.86328125" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" customWidth="1"/>
-    <col min="3" max="3" width="14.06640625" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="11.87890625" customWidth="1"/>
+    <col min="2" max="2" width="18.5859375" customWidth="1"/>
+    <col min="3" max="3" width="14.05859375" customWidth="1"/>
+    <col min="5" max="5" width="14.3515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -584,7 +584,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -601,7 +601,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -618,7 +618,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>

--- a/power-apps-challenge/power-apps-challenge.xlsx
+++ b/power-apps-challenge/power-apps-challenge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\first-steps-with-power-apps-for-excel-users\power-apps-challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25047E42-9F93-4A53-BF61-E2254A4E6A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5088E460-9382-4996-A89D-4C0A449069C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,21 +79,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
-    <t>Property ID</t>
-  </si>
-  <si>
-    <t>Description of issue</t>
-  </si>
-  <si>
-    <t>Date reported</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Image of issue</t>
-  </si>
-  <si>
     <t>P001</t>
   </si>
   <si>
@@ -125,6 +113,18 @@
   </si>
   <si>
     <t>Clogged drain</t>
+  </si>
+  <si>
+    <t>PropertyID</t>
+  </si>
+  <si>
+    <t>DescriptionOfIssue</t>
+  </si>
+  <si>
+    <t>DateReported</t>
+  </si>
+  <si>
+    <t>ImageOfIssue</t>
   </si>
 </sst>
 </file>
@@ -268,11 +268,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}" name="claims" displayName="claims" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{55F8BFD6-C4FC-4C00-B089-DA9A0648BD4A}" name="Property ID"/>
-    <tableColumn id="2" xr3:uid="{F8DABAC4-7AD7-4CA1-A284-286C9E0846F9}" name="Description of issue"/>
-    <tableColumn id="3" xr3:uid="{4B3F3E4E-27F9-4E22-BABA-49870B619933}" name="Date reported"/>
+    <tableColumn id="1" xr3:uid="{55F8BFD6-C4FC-4C00-B089-DA9A0648BD4A}" name="PropertyID"/>
+    <tableColumn id="2" xr3:uid="{F8DABAC4-7AD7-4CA1-A284-286C9E0846F9}" name="DescriptionOfIssue"/>
+    <tableColumn id="3" xr3:uid="{4B3F3E4E-27F9-4E22-BABA-49870B619933}" name="DateReported"/>
     <tableColumn id="4" xr3:uid="{E8864757-D816-4E54-B626-6D5CD61F85F3}" name="Status"/>
-    <tableColumn id="5" xr3:uid="{C41BDAFA-328D-4180-B731-9DEF69BFBCE3}" name="Image of issue"/>
+    <tableColumn id="5" xr3:uid="{C41BDAFA-328D-4180-B731-9DEF69BFBCE3}" name="ImageOfIssue"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -552,33 +552,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>44936</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="e" vm="1">
         <v>#VALUE!</v>
@@ -586,16 +586,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2">
         <v>44938</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="e" vm="2">
         <v>#VALUE!</v>
@@ -603,16 +603,16 @@
     </row>
     <row r="4" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2">
         <v>44941</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="e" vm="3">
         <v>#VALUE!</v>
@@ -620,16 +620,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>44944</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="e" vm="4">
         <v>#VALUE!</v>
